--- a/artfynd/A 61037-2024 artfynd.xlsx
+++ b/artfynd/A 61037-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69468413</v>
+        <v>199349</v>
       </c>
       <c r="B2" t="n">
-        <v>104456</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>107574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Kyrketorp, Abrahamsgården, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422682.8098105517</v>
+        <v>422683</v>
       </c>
       <c r="R2" t="n">
-        <v>6456811.732134615</v>
+        <v>6456812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,26 +745,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Senaste fyndet 2003.</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -778,19 +770,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Ingvar Claesson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Ingvar Claesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Uppföljning stor ögontröst, Västra Götaland</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
